--- a/sheets/민요/검수/매화 타령.xlsx
+++ b/sheets/민요/검수/매화 타령.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,42 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1956,8 +2072,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:U14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -1980,736 +2100,599 @@
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">매화 타령 — 민요채보-3/매화 타령.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">매화 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+      <c s="8" r="R2"/>
+      <c s="8" r="S2"/>
+      <c s="8" r="T2"/>
+      <c s="8" r="U2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 汰</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">떨떨</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="E3" s="15"/>
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G3" s="15"/>
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">나돌아</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">무삼</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 汰</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">어저께</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">인간이</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="T3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="U3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">좋구나</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="13"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">거리고</t>
         </is>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="F4" s="13"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="17"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="13"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="18"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="18"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="18"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="15"/>
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">나돌아</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" s="16"/>
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">나돌아</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">양치로</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">밤에는</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">별만</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="R6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="S6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">에헤에</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="T6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="U6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">매화</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="13"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">가네</t>
         </is>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="F7" s="13"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="K7" s="17"/>
+      <c r="L7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">삼승</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">구경</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="Q7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">사중에</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="R7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="S7" s="17"/>
+      <c r="T7" s="13"/>
+      <c r="U7" s="17"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="13"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="18"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="18"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑
 仲</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="C9" s="15"/>
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="E9" s="16"/>
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" s="16"/>
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I9" s="15"/>
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">버선에</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 仲</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">가고</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="Q9" s="15"/>
+      <c r="R9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="S9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">디여라</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="T9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="U9" s="2" t="inlineStr">
+      <c r="U9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">로구나</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="13"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="13"/>
+      <c r="U10" s="17"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="13"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="18"/>
+      <c r="T11" s="13"/>
+      <c r="U11" s="18"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="13"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="15"/>
+      <c r="R12" s="13"/>
+      <c r="S12" s="15"/>
+      <c r="T12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="U12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="13"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="13"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="13"/>
+      <c r="U13" s="17"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="13"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="18"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="18"/>
+      <c r="T14" s="13"/>
+      <c r="U14" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:U2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="61"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/매화 타령.xlsx
+++ b/sheets/민요/검수/매화 타령.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -778,13 +778,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -853,13 +853,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -932,13 +932,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1011,13 +1011,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I15" s="2"/>
@@ -1169,13 +1169,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1323,13 +1323,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1402,13 +1402,13 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1710,13 +1710,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1785,13 +1785,13 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2022,13 +2022,13 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2097,13 +2097,13 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2255,13 +2255,13 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2654,13 +2654,13 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2970,13 +2970,13 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3045,13 +3045,13 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3203,13 +3203,13 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3599,13 +3599,13 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -3674,13 +3674,13 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -3982,13 +3982,13 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I91" s="2"/>
@@ -4057,13 +4057,13 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―</t>
+          <t xml:space="preserve">–|–</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="I92" s="2"/>
@@ -4128,13 +4128,13 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―</t>
+          <t xml:space="preserve">–|–</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="I94" s="3"/>
@@ -4207,13 +4207,13 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―</t>
+          <t xml:space="preserve">–|–</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="I96" s="3"/>
@@ -4286,13 +4286,13 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       <c r="B3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -4644,7 +4644,7 @@
       <c r="D3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
@@ -4655,7 +4655,7 @@
       <c r="F3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
@@ -4677,7 +4677,7 @@
       <c r="J3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="K3" s="8" t="inlineStr">
@@ -4688,7 +4688,7 @@
       <c r="L3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr">
@@ -4941,7 +4941,7 @@
       <c r="F7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -4974,7 +4974,7 @@
       <c r="L7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
@@ -5101,7 +5101,7 @@
       <c r="H9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -5112,7 +5112,7 @@
       <c r="J9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr">
@@ -5123,7 +5123,7 @@
       <c r="L9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
@@ -5134,7 +5134,7 @@
       <c r="N9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="O9" s="9" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -5208,7 +5208,7 @@
       <c r="D11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -5241,7 +5241,7 @@
       <c r="J11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
@@ -5263,7 +5263,7 @@
       <c r="N11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="O11" s="8" t="inlineStr">
@@ -5278,7 +5278,7 @@
       <c r="C12" s="9"/>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E12" s="9"/>
@@ -5339,8 +5339,8 @@
       <c r="C13" s="9"/>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="E13" s="9"/>
@@ -5391,7 +5391,7 @@
       <c r="N13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="O13" s="9" t="inlineStr">
@@ -5463,8 +5463,8 @@
       <c r="C15" s="8"/>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="E15" s="11"/>
@@ -5493,7 +5493,7 @@
       <c r="J15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr">
@@ -5515,7 +5515,7 @@
       <c r="N15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="O15" s="8" t="inlineStr">
@@ -5572,7 +5572,7 @@
       <c r="M16" s="9"/>
       <c r="N16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O16" s="9"/>
@@ -5583,15 +5583,15 @@
       <c r="C17" s="9"/>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -5602,7 +5602,7 @@
       <c r="H17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
@@ -5624,7 +5624,7 @@
       <c r="L17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="M17" s="9" t="inlineStr">

--- a/sheets/민요/검수/매화 타령.xlsx
+++ b/sheets/민요/검수/매화 타령.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4609,100 +4650,100 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">매화 타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –無</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">떨</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢無</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어저</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –無</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좋구</t>
         </is>
@@ -4710,64 +4751,64 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">떨</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="23"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">께</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="M4" s="23"/>
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4775,75 +4816,75 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">거리</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無南</t>
         </is>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="23"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">영치</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">방에</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 ·</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="M5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無南</t>
         </is>
       </c>
-      <c r="O5" s="9" t="inlineStr">
+      <c r="O5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">매화</t>
         </is>
@@ -4851,144 +4892,144 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="24"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="K6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">별</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr">
+      <c r="M6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="O6" s="10"/>
+      <c r="O6" s="24"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나돌</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나돌</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無南</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">구경</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無南</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">만사</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –無</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="M7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲姑</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="O7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">로오</t>
         </is>
@@ -4996,148 +5037,148 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">승</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">중</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="M8" s="9" t="inlineStr">
+      <c r="M8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O8" s="9"/>
+      <c r="O8" s="23"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無南</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲姑</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南南
 南</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">버선에</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –無</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">디여</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="O9" s="9" t="inlineStr">
+      <c r="O9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5145,128 +5186,128 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="24"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="24"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="K10" s="24"/>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="M10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O10" s="10"/>
+      <c r="O10" s="24"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">불받</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢無</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">그저</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –無</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">독</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M11" s="8" t="inlineStr">
+      <c r="M11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">사랑</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="O11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5274,60 +5315,60 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="B12" s="21"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="23"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">께</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="K12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M12" s="9" t="inlineStr">
+      <c r="M12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O12" s="9" t="inlineStr">
+      <c r="O12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -5335,66 +5376,66 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="B13" s="21"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="23"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌㴌
 㴌</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">달라</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">방에</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">공방</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無南</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">계화</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="O13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
@@ -5402,56 +5443,56 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="B14" s="21"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="E14" s="24"/>
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">느냐</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="K14" s="10" t="inlineStr">
+      <c r="K14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="M14" s="24"/>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O14" s="10" t="inlineStr">
+      <c r="O14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -5459,66 +5500,66 @@
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="E15" s="27"/>
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑
 南</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나돌</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無南</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">구경</t>
         </is>
       </c>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="J15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="L15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 仲姑</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">로오</t>
         </is>
       </c>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="N15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="O15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5526,119 +5567,119 @@
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="B16" s="21"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="E16" s="28"/>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="J16" s="17" t="inlineStr">
+      <c r="J16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="L16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M16" s="9"/>
-      <c r="N16" s="17" t="inlineStr">
+      <c r="M16" s="23"/>
+      <c r="N16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O16" s="9"/>
+      <c r="O16" s="23"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="B17" s="21"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="E17" s="28"/>
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="J17" s="18" t="inlineStr">
+      <c r="J17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
 無潢</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr">
+      <c r="K17" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">날이</t>
         </is>
       </c>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="M17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="N17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無南</t>
         </is>
       </c>
-      <c r="O17" s="9" t="inlineStr">
+      <c r="O17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">에헤</t>
         </is>
@@ -5646,48 +5687,48 @@
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="B18" s="21"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="E18" s="26"/>
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="G18" s="24"/>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="I18" s="24"/>
+      <c r="J18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="K18" s="10" t="inlineStr">
+      <c r="K18" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">란다</t>
         </is>
       </c>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="L18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="M18" s="10"/>
-      <c r="N18" s="18" t="inlineStr">
+      <c r="M18" s="24"/>
+      <c r="N18" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="O18" s="13" t="inlineStr">
+      <c r="O18" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>

--- a/sheets/민요/검수/매화 타령.xlsx
+++ b/sheets/민요/검수/매화 타령.xlsx
@@ -4629,26 +4629,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E4" s="23"/>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M4" s="23"/>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
       <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-·</t>
+–</t>
         </is>
       </c>
       <c r="M5" s="23" t="inlineStr">
@@ -4890,7 +4890,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="O6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="O8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="O10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -5313,7 +5313,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -5441,7 +5441,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -5498,7 +5498,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -5565,7 +5565,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="O16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -5685,7 +5685,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="24"/>

--- a/sheets/민요/검수/매화 타령.xlsx
+++ b/sheets/민요/검수/매화 타령.xlsx
@@ -1791,12 +1791,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I33" s="2"/>
@@ -3051,12 +3051,12 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I65" s="2"/>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I81" s="2"/>
@@ -5697,13 +5697,13 @@
       <c r="E18" s="26"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G18" s="24"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I18" s="24"/>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="L18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M18" s="24"/>

--- a/sheets/민요/검수/매화 타령.xlsx
+++ b/sheets/민요/검수/매화 타령.xlsx
@@ -4712,7 +4712,8 @@
       </c>
       <c r="I3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">어저</t>
+          <t xml:space="preserve">어
+저</t>
         </is>
       </c>
       <c r="J3" s="21" t="inlineStr">
@@ -4745,7 +4746,8 @@
       </c>
       <c r="O3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">좋구</t>
+          <t xml:space="preserve">좋
+구</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4826,8 @@
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">거리</t>
+          <t xml:space="preserve">거
+리</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -4842,7 +4845,8 @@
       </c>
       <c r="G5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">영치</t>
+          <t xml:space="preserve">영
+치</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -4853,7 +4857,8 @@
       </c>
       <c r="I5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">방에</t>
+          <t xml:space="preserve">방
+에</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -4886,7 +4891,8 @@
       </c>
       <c r="O5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">매화</t>
+          <t xml:space="preserve">매
+화</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4971,8 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">나돌</t>
+          <t xml:space="preserve">나
+돌</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -4976,7 +4983,8 @@
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">나돌</t>
+          <t xml:space="preserve">나
+돌</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -4998,7 +5006,8 @@
       </c>
       <c r="I7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">구경</t>
+          <t xml:space="preserve">구
+경</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -5009,7 +5018,8 @@
       </c>
       <c r="K7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">만사</t>
+          <t xml:space="preserve">만
+사</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -5031,7 +5041,8 @@
       </c>
       <c r="O7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">로오</t>
+          <t xml:space="preserve">로
+오</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5147,9 @@
       </c>
       <c r="G9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">버선에</t>
+          <t xml:space="preserve">버
+선
+에</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -5169,7 +5182,8 @@
       </c>
       <c r="M9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">디여</t>
+          <t xml:space="preserve">디
+여</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
@@ -5265,7 +5279,8 @@
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">불받</t>
+          <t xml:space="preserve">불
+받</t>
         </is>
       </c>
       <c r="H11" s="25" t="inlineStr">
@@ -5276,7 +5291,8 @@
       </c>
       <c r="I11" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">그저</t>
+          <t xml:space="preserve">그
+저</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -5298,7 +5314,8 @@
       </c>
       <c r="M11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">사랑</t>
+          <t xml:space="preserve">사
+랑</t>
         </is>
       </c>
       <c r="N11" s="21" t="inlineStr">
@@ -5393,7 +5410,8 @@
       </c>
       <c r="G13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">달라</t>
+          <t xml:space="preserve">달
+라</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -5404,7 +5422,8 @@
       </c>
       <c r="I13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">방에</t>
+          <t xml:space="preserve">방
+에</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -5415,7 +5434,8 @@
       </c>
       <c r="K13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">공방</t>
+          <t xml:space="preserve">공
+방</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -5426,7 +5446,8 @@
       </c>
       <c r="M13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">계화</t>
+          <t xml:space="preserve">계
+화</t>
         </is>
       </c>
       <c r="N13" s="21" t="inlineStr">
@@ -5458,7 +5479,8 @@
       </c>
       <c r="G14" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">느냐</t>
+          <t xml:space="preserve">느
+냐</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -5517,7 +5539,8 @@
       </c>
       <c r="G15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">나돌</t>
+          <t xml:space="preserve">나
+돌</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -5528,7 +5551,8 @@
       </c>
       <c r="I15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">구경</t>
+          <t xml:space="preserve">구
+경</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -5550,7 +5574,8 @@
       </c>
       <c r="M15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">로오</t>
+          <t xml:space="preserve">로
+오</t>
         </is>
       </c>
       <c r="N15" s="21" t="inlineStr">
@@ -5659,7 +5684,8 @@
       </c>
       <c r="K17" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">날이</t>
+          <t xml:space="preserve">날
+이</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -5681,7 +5707,8 @@
       </c>
       <c r="O17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">에헤</t>
+          <t xml:space="preserve">에
+헤</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5741,8 @@
       </c>
       <c r="K18" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">란다</t>
+          <t xml:space="preserve">란
+다</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">

--- a/sheets/민요/검수/매화 타령.xlsx
+++ b/sheets/민요/검수/매화 타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4677,7 +4700,7 @@
 –無</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">떨</t>
         </is>
@@ -4688,7 +4711,7 @@
 –</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -4699,7 +4722,7 @@
 –</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
@@ -4710,7 +4733,7 @@
 潢無</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어
 저</t>
@@ -4722,7 +4745,7 @@
 –無</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
@@ -4733,7 +4756,7 @@
 –</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4744,7 +4767,7 @@
 姑</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">좋
 구</t>
@@ -4758,7 +4781,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">떨</t>
         </is>
@@ -4768,13 +4791,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -4784,7 +4807,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I4" s="23" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">께</t>
         </is>
@@ -4794,7 +4817,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K4" s="23" t="inlineStr">
+      <c r="K4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
@@ -4804,13 +4827,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M4" s="23"/>
+      <c r="M4" s="30"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O4" s="23" t="inlineStr">
+      <c r="O4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4824,7 +4847,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">거
 리</t>
@@ -4836,14 +4859,14 @@
 無南</t>
         </is>
       </c>
-      <c r="E5" s="23"/>
+      <c r="E5" s="30"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="G5" s="23" t="inlineStr">
+      <c r="G5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">영
 치</t>
@@ -4855,7 +4878,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I5" s="23" t="inlineStr">
+      <c r="I5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">방
 에</t>
@@ -4867,7 +4890,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K5" s="23" t="inlineStr">
+      <c r="K5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4878,7 +4901,7 @@
 –</t>
         </is>
       </c>
-      <c r="M5" s="23" t="inlineStr">
+      <c r="M5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4889,7 +4912,7 @@
 無南</t>
         </is>
       </c>
-      <c r="O5" s="23" t="inlineStr">
+      <c r="O5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">매
 화</t>
@@ -4903,7 +4926,7 @@
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -4913,13 +4936,13 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E6" s="24"/>
+      <c r="E6" s="31"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -4929,7 +4952,7 @@
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr">
+      <c r="I6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4939,7 +4962,7 @@
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="K6" s="24" t="inlineStr">
+      <c r="K6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">별</t>
         </is>
@@ -4949,7 +4972,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M6" s="24" t="inlineStr">
+      <c r="M6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
@@ -4959,7 +4982,7 @@
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="O6" s="24"/>
+      <c r="O6" s="31"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
@@ -4969,7 +4992,7 @@
 南</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나
 돌</t>
@@ -4981,7 +5004,7 @@
 姑</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나
 돌</t>
@@ -4993,7 +5016,7 @@
 –</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -5004,7 +5027,7 @@
 無南</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">구
 경</t>
@@ -5016,7 +5039,7 @@
 無南</t>
         </is>
       </c>
-      <c r="K7" s="22" t="inlineStr">
+      <c r="K7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">만
 사</t>
@@ -5028,7 +5051,7 @@
 –無</t>
         </is>
       </c>
-      <c r="M7" s="22" t="inlineStr">
+      <c r="M7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5039,7 +5062,7 @@
 仲姑</t>
         </is>
       </c>
-      <c r="O7" s="22" t="inlineStr">
+      <c r="O7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">로
 오</t>
@@ -5053,7 +5076,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5063,7 +5086,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5073,7 +5096,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">승</t>
         </is>
@@ -5083,7 +5106,7 @@
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="I8" s="23" t="inlineStr">
+      <c r="I8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -5093,7 +5116,7 @@
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="K8" s="23" t="inlineStr">
+      <c r="K8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">중</t>
         </is>
@@ -5103,7 +5126,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="M8" s="23" t="inlineStr">
+      <c r="M8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
@@ -5113,7 +5136,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O8" s="23"/>
+      <c r="O8" s="30"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
@@ -5123,7 +5146,7 @@
 無南</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -5134,7 +5157,7 @@
 仲姑</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -5145,7 +5168,7 @@
 南</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">버
 선
@@ -5158,7 +5181,7 @@
 –</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="I9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -5169,7 +5192,7 @@
 –</t>
         </is>
       </c>
-      <c r="K9" s="23" t="inlineStr">
+      <c r="K9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5180,7 +5203,7 @@
 –無</t>
         </is>
       </c>
-      <c r="M9" s="23" t="inlineStr">
+      <c r="M9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">디
 여</t>
@@ -5192,7 +5215,7 @@
 –</t>
         </is>
       </c>
-      <c r="O9" s="23" t="inlineStr">
+      <c r="O9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5205,7 +5228,7 @@
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -5215,7 +5238,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5226,25 +5249,25 @@
 △</t>
         </is>
       </c>
-      <c r="G10" s="24"/>
+      <c r="G10" s="31"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I10" s="24"/>
+      <c r="I10" s="31"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K10" s="24"/>
+      <c r="K10" s="31"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M10" s="24" t="inlineStr">
+      <c r="M10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -5254,19 +5277,19 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O10" s="24"/>
+      <c r="O10" s="31"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
-      <c r="C11" s="22"/>
+      <c r="C11" s="29"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -5277,7 +5300,7 @@
 南</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">불
 받</t>
@@ -5289,7 +5312,7 @@
 潢無</t>
         </is>
       </c>
-      <c r="I11" s="27" t="inlineStr">
+      <c r="I11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">그
 저</t>
@@ -5301,7 +5324,7 @@
 –無</t>
         </is>
       </c>
-      <c r="K11" s="22" t="inlineStr">
+      <c r="K11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">독</t>
         </is>
@@ -5312,7 +5335,7 @@
 姑</t>
         </is>
       </c>
-      <c r="M11" s="22" t="inlineStr">
+      <c r="M11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">사
 랑</t>
@@ -5324,7 +5347,7 @@
 –</t>
         </is>
       </c>
-      <c r="O11" s="22" t="inlineStr">
+      <c r="O11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5333,19 +5356,19 @@
     <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
-      <c r="C12" s="23"/>
+      <c r="C12" s="30"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E12" s="23"/>
+      <c r="E12" s="30"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5355,7 +5378,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I12" s="23" t="inlineStr">
+      <c r="I12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">께</t>
         </is>
@@ -5365,7 +5388,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K12" s="23" t="inlineStr">
+      <c r="K12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
@@ -5375,7 +5398,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M12" s="23" t="inlineStr">
+      <c r="M12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -5385,7 +5408,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O12" s="23" t="inlineStr">
+      <c r="O12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -5394,21 +5417,21 @@
     <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
-      <c r="C13" s="23"/>
+      <c r="C13" s="30"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="E13" s="23"/>
+      <c r="E13" s="30"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌㴌
 㴌</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
+      <c r="G13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">달
 라</t>
@@ -5420,7 +5443,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I13" s="23" t="inlineStr">
+      <c r="I13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">방
 에</t>
@@ -5432,7 +5455,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K13" s="23" t="inlineStr">
+      <c r="K13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">공
 방</t>
@@ -5444,7 +5467,7 @@
 無南</t>
         </is>
       </c>
-      <c r="M13" s="23" t="inlineStr">
+      <c r="M13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">계
 화</t>
@@ -5456,7 +5479,7 @@
 –</t>
         </is>
       </c>
-      <c r="O13" s="23" t="inlineStr">
+      <c r="O13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
@@ -5465,19 +5488,19 @@
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
-      <c r="C14" s="24"/>
+      <c r="C14" s="31"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E14" s="24"/>
+      <c r="E14" s="31"/>
       <c r="F14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="G14" s="26" t="inlineStr">
+      <c r="G14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">느
 냐</t>
@@ -5488,7 +5511,7 @@
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="I14" s="24" t="inlineStr">
+      <c r="I14" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -5498,7 +5521,7 @@
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="K14" s="24" t="inlineStr">
+      <c r="K14" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5508,13 +5531,13 @@
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="M14" s="24"/>
+      <c r="M14" s="31"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O14" s="24" t="inlineStr">
+      <c r="O14" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -5523,21 +5546,21 @@
     <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
-      <c r="C15" s="22"/>
+      <c r="C15" s="29"/>
       <c r="D15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="E15" s="27"/>
+      <c r="E15" s="33"/>
       <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑
 南</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나
 돌</t>
@@ -5549,7 +5572,7 @@
 無南</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">구
 경</t>
@@ -5561,7 +5584,7 @@
 –</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="K15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
@@ -5572,7 +5595,7 @@
 仲姑</t>
         </is>
       </c>
-      <c r="M15" s="22" t="inlineStr">
+      <c r="M15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">로
 오</t>
@@ -5584,7 +5607,7 @@
 –</t>
         </is>
       </c>
-      <c r="O15" s="22" t="inlineStr">
+      <c r="O15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5593,19 +5616,19 @@
     <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
-      <c r="C16" s="23"/>
+      <c r="C16" s="30"/>
       <c r="D16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E16" s="28"/>
+      <c r="E16" s="34"/>
       <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G16" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5615,7 +5638,7 @@
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="I16" s="23" t="inlineStr">
+      <c r="I16" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -5625,7 +5648,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K16" s="23" t="inlineStr">
+      <c r="K16" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -5635,32 +5658,32 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M16" s="23"/>
+      <c r="M16" s="30"/>
       <c r="N16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O16" s="23"/>
+      <c r="O16" s="30"/>
     </row>
     <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
-      <c r="C17" s="23"/>
+      <c r="C17" s="30"/>
       <c r="D17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="E17" s="28"/>
+      <c r="E17" s="34"/>
       <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="G17" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -5671,7 +5694,7 @@
 –</t>
         </is>
       </c>
-      <c r="I17" s="23" t="inlineStr">
+      <c r="I17" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -5682,7 +5705,7 @@
 無潢</t>
         </is>
       </c>
-      <c r="K17" s="28" t="inlineStr">
+      <c r="K17" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">날
 이</t>
@@ -5694,7 +5717,7 @@
 –</t>
         </is>
       </c>
-      <c r="M17" s="23" t="inlineStr">
+      <c r="M17" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5705,7 +5728,7 @@
 無南</t>
         </is>
       </c>
-      <c r="O17" s="23" t="inlineStr">
+      <c r="O17" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">에
 헤</t>
@@ -5715,31 +5738,31 @@
     <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
-      <c r="C18" s="24"/>
+      <c r="C18" s="31"/>
       <c r="D18" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E18" s="26"/>
+      <c r="E18" s="32"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G18" s="24"/>
+      <c r="G18" s="31"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I18" s="24"/>
+      <c r="I18" s="31"/>
       <c r="J18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="K18" s="24" t="inlineStr">
+      <c r="K18" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">란
 다</t>
@@ -5750,13 +5773,13 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="M18" s="24"/>
+      <c r="M18" s="31"/>
       <c r="N18" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="O18" s="26" t="inlineStr">
+      <c r="O18" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>

--- a/sheets/민요/검수/매화 타령.xlsx
+++ b/sheets/민요/검수/매화 타령.xlsx
@@ -724,10 +724,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/매화 타령.xlsx
+++ b/sheets/민요/검수/매화 타령.xlsx
@@ -670,17 +670,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -797,7 +797,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -855,6 +855,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2941,368 +2985,368 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:O10"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="60.61" customHeight="true">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="135.3" customHeight="true">
+      <c r="B3" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="19" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="135.3" customHeight="true">
+      <c r="B4" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="22"/>
+      <c r="F4" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="O4" s="9" t="s">
+      <c r="O4" s="20" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="135.3" customHeight="true">
+      <c r="B5" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="M5" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="O5" s="9" t="s">
+      <c r="O5" s="20" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="10" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="135.3" customHeight="true">
+      <c r="B6" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="K6" s="13" t="s">
+      <c r="K6" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="L6" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="O6" s="13" t="s">
+      <c r="O6" s="24" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="10" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="135.3" customHeight="true">
+      <c r="B7" s="18"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="M7" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="O7" s="19" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="135.3" customHeight="true">
+      <c r="B8" s="18"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="7" t="s">
+      <c r="E8" s="20"/>
+      <c r="F8" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="M8" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="O8" s="9" t="s">
+      <c r="O8" s="20" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="7" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="135.3" customHeight="true">
+      <c r="B9" s="18"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="K9" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="M9" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="O9" s="9" t="s">
+      <c r="O9" s="20" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="135.3" customHeight="true">
+      <c r="B10" s="18"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="K10" s="13" t="s">
+      <c r="K10" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="M10" s="13" t="s">
+      <c r="M10" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="N10" s="10" t="s">
+      <c r="N10" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="O10" s="12" t="s">
+      <c r="O10" s="23" t="s">
         <v>174</v>
       </c>
     </row>
@@ -3312,7 +3356,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="86" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/매화 타령.xlsx
+++ b/sheets/민요/검수/매화 타령.xlsx
@@ -2991,24 +2991,24 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="60.61" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="56.34" customHeight="true">
       <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
@@ -3026,7 +3026,7 @@
       <c r="N2" s="17"/>
       <c r="O2" s="17"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="135.3" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="125.72" customHeight="true">
       <c r="B3" s="18" t="s">
         <v>76</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="135.3" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="125.72" customHeight="true">
       <c r="B4" s="18" t="s">
         <v>87</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="135.3" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="125.72" customHeight="true">
       <c r="B5" s="18" t="s">
         <v>111</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="135.3" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="125.72" customHeight="true">
       <c r="B6" s="21" t="s">
         <v>67</v>
       </c>
@@ -3200,7 +3200,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="135.3" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="125.72" customHeight="true">
       <c r="B7" s="18"/>
       <c r="C7" s="19"/>
       <c r="D7" s="21" t="s">
@@ -3240,7 +3240,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="135.3" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="125.72" customHeight="true">
       <c r="B8" s="18"/>
       <c r="C8" s="20"/>
       <c r="D8" s="18" t="s">
@@ -3278,7 +3278,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="135.3" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="125.72" customHeight="true">
       <c r="B9" s="18"/>
       <c r="C9" s="20"/>
       <c r="D9" s="21"/>
@@ -3314,7 +3314,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="135.3" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="125.72" customHeight="true">
       <c r="B10" s="18"/>
       <c r="C10" s="24"/>
       <c r="D10" s="21"/>
@@ -3356,7 +3356,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="71"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
